--- a/data/file_generation/input/data_221/2025-2026学年上学期七年级学生名单(1).xlsx
+++ b/data/file_generation/input/data_221/2025-2026学年上学期七年级学生名单(1).xlsx
@@ -12103,18 +12103,26 @@
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
+  <documentManagement>
+    <SharedWithUsers xmlns="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AEDBC24C-4DD4-4D58-A88C-E3353063050C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{648A5810-412D-4369-94DD-9A5FB3637C49}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DA364DEC-20C0-4AE6-AD1B-7E767F6498A5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BBF3256-FD95-4BEA-A3B9-75160537DA4D}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AB2EA434-2DA6-419B-A3D1-90C66F62CA1B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D0582054-2073-4F91-94BF-5EF12C269897}"/>
 </file>